--- a/Resources/Review/Flagged Variable Recoding Operations.xlsx
+++ b/Resources/Review/Flagged Variable Recoding Operations.xlsx
@@ -1057,7 +1057,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>7</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -1072,7 +1072,7 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2018,2024</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
